--- a/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Forecast_Series_h1.xlsx
+++ b/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Forecast_Series_h1.xlsx
@@ -459,22 +459,22 @@
         <v>0.2250000000000085</v>
       </c>
       <c r="D2">
-        <v>0.5404405835808165</v>
+        <v>0.4199859408521097</v>
       </c>
       <c r="E2">
         <v>-1.303044651843698</v>
       </c>
       <c r="F2">
-        <v>-0.9876040682628905</v>
+        <v>-1.108058710991597</v>
       </c>
       <c r="G2">
-        <v>-0.315440583580808</v>
+        <v>-0.1949859408521012</v>
       </c>
       <c r="H2">
-        <v>-0.315440583580808</v>
+        <v>-0.1949859408521011</v>
       </c>
       <c r="I2">
-        <v>-0.7225635690490533</v>
+        <v>-0.470131257694105</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -497,22 +497,22 @@
         <v>0.25</v>
       </c>
       <c r="D3">
-        <v>0.5596322435650039</v>
+        <v>0.6218563394626684</v>
       </c>
       <c r="E3">
         <v>0.7744122965641937</v>
       </c>
       <c r="F3">
-        <v>1.084044540129198</v>
+        <v>1.146268636026862</v>
       </c>
       <c r="G3">
-        <v>-0.3096322435650039</v>
+        <v>-0.3718563394626684</v>
       </c>
       <c r="H3">
-        <v>0.3096322435650039</v>
+        <v>0.3718563394626684</v>
       </c>
       <c r="I3">
-        <v>0.5754381599140946</v>
+        <v>0.7142173808690541</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -535,22 +535,22 @@
         <v>-0.6500000000000057</v>
       </c>
       <c r="D4">
-        <v>0.5106378678060506</v>
+        <v>0.2090845912122806</v>
       </c>
       <c r="E4">
         <v>3.150762010965521</v>
       </c>
       <c r="F4">
-        <v>4.311399878771578</v>
+        <v>4.009846602177808</v>
       </c>
       <c r="G4">
-        <v>-1.160637867806056</v>
+        <v>-0.8590845912122863</v>
       </c>
       <c r="H4">
-        <v>1.160637867806057</v>
+        <v>0.8590845912122864</v>
       </c>
       <c r="I4">
-        <v>8.660867664928082</v>
+        <v>6.151568523253415</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -573,22 +573,22 @@
         <v>0.2000000000000028</v>
       </c>
       <c r="D5">
-        <v>0.1235664191002112</v>
+        <v>-3.466827857782311</v>
       </c>
       <c r="E5">
         <v>-0.5280390842034699</v>
       </c>
       <c r="F5">
-        <v>-0.6044726651032616</v>
+        <v>-4.194866941985784</v>
       </c>
       <c r="G5">
-        <v>0.07643358089979159</v>
+        <v>3.666827857782314</v>
       </c>
       <c r="H5">
-        <v>0.07643358089979169</v>
+        <v>3.666827857782314</v>
       </c>
       <c r="I5">
-        <v>0.08656192841060067</v>
+        <v>17.31808338651872</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -611,31 +611,31 @@
         <v>0.4200000000000017</v>
       </c>
       <c r="D6">
-        <v>0.4994292558307422</v>
+        <v>0.3313095025176546</v>
       </c>
       <c r="E6">
         <v>0.2586484434320426</v>
       </c>
       <c r="F6">
-        <v>0.3380776992627831</v>
+        <v>0.1699579459496955</v>
       </c>
       <c r="G6">
-        <v>-0.07942925583074051</v>
+        <v>0.08869049748234709</v>
       </c>
       <c r="H6">
-        <v>0.07942925583074045</v>
+        <v>-0.08869049748234711</v>
       </c>
       <c r="I6">
-        <v>0.04739751344899826</v>
+        <v>-0.03801331389837893</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -649,22 +649,22 @@
         <v>0.4999999999999858</v>
       </c>
       <c r="D7">
-        <v>0.4643522996338431</v>
+        <v>0.2038123374423979</v>
       </c>
       <c r="E7">
         <v>-0.198016164584883</v>
       </c>
       <c r="F7">
-        <v>-0.2336638649510257</v>
+        <v>-0.4942038271424709</v>
       </c>
       <c r="G7">
-        <v>0.03564770036614268</v>
+        <v>0.2961876625575879</v>
       </c>
       <c r="H7">
-        <v>0.03564770036614268</v>
+        <v>0.2961876625575879</v>
       </c>
       <c r="I7">
-        <v>0.01538840034694369</v>
+        <v>0.2050270213253578</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -687,22 +687,22 @@
         <v>0.3</v>
       </c>
       <c r="D8">
-        <v>0.5172123736136406</v>
+        <v>0.4103097124520395</v>
       </c>
       <c r="E8">
         <v>-1.199182264219509</v>
       </c>
       <c r="F8">
-        <v>-0.9819698906058684</v>
+        <v>-1.088872551767469</v>
       </c>
       <c r="G8">
-        <v>-0.2172123736136406</v>
+        <v>-0.1103097124520395</v>
       </c>
       <c r="H8">
-        <v>-0.2172123736136405</v>
+        <v>-0.1103097124520396</v>
       </c>
       <c r="I8">
-        <v>-0.4737732367621269</v>
+        <v>-0.2523946688260279</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -725,22 +725,22 @@
         <v>0.5</v>
       </c>
       <c r="D9">
-        <v>0.5559532276938891</v>
+        <v>0.5427295426160457</v>
       </c>
       <c r="E9">
         <v>-0.00301810865190888</v>
       </c>
       <c r="F9">
-        <v>0.05293511904198023</v>
+        <v>0.03971143396413679</v>
       </c>
       <c r="G9">
-        <v>-0.05595322769388911</v>
+        <v>-0.04272954261604567</v>
       </c>
       <c r="H9">
-        <v>0.04991701039007135</v>
+        <v>0.03669332531222791</v>
       </c>
       <c r="I9">
-        <v>0.002793017848153891</v>
+        <v>0.00156788900765327</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -763,22 +763,22 @@
         <v>0.1</v>
       </c>
       <c r="D10">
-        <v>0.4980839566216836</v>
+        <v>0.3471822841278672</v>
       </c>
       <c r="E10">
         <v>-0.4101576022592716</v>
       </c>
       <c r="F10">
-        <v>-0.01207364563758795</v>
+        <v>-0.1629753181314043</v>
       </c>
       <c r="G10">
-        <v>-0.3980839566216836</v>
+        <v>-0.2471822841278672</v>
       </c>
       <c r="H10">
-        <v>-0.3980839566216836</v>
+        <v>-0.2471822841278672</v>
       </c>
       <c r="I10">
-        <v>-0.1680834857720928</v>
+        <v>-0.1416683043710424</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -801,22 +801,22 @@
         <v>0.1</v>
       </c>
       <c r="D11">
-        <v>0.4929538241353998</v>
+        <v>0.3257825290890698</v>
       </c>
       <c r="E11">
         <v>-0.133981281497472</v>
       </c>
       <c r="F11">
-        <v>0.2589725426379278</v>
+        <v>0.0918012475915978</v>
       </c>
       <c r="G11">
-        <v>-0.3929538241353998</v>
+        <v>-0.2257825290890698</v>
       </c>
       <c r="H11">
-        <v>0.1249912611404558</v>
+        <v>-0.04218003390587419</v>
       </c>
       <c r="I11">
-        <v>0.04911579404864849</v>
+        <v>-0.00952351473233099</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -825,7 +825,7 @@
         <v>1</v>
       </c>
       <c r="L11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -839,22 +839,22 @@
         <v>0.2</v>
       </c>
       <c r="D12">
-        <v>0.4780607639075022</v>
+        <v>0.2823630897464367</v>
       </c>
       <c r="E12">
         <v>0.1367145827682783</v>
       </c>
       <c r="F12">
-        <v>0.4147753466757805</v>
+        <v>0.219077672514715</v>
       </c>
       <c r="G12">
-        <v>-0.2780607639075022</v>
+        <v>-0.08236308974643669</v>
       </c>
       <c r="H12">
-        <v>0.2780607639075022</v>
+        <v>0.08236308974643669</v>
       </c>
       <c r="I12">
-        <v>0.1533477110685095</v>
+        <v>0.02930414945296029</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -877,28 +877,28 @@
         <v>0.4200000000000017</v>
       </c>
       <c r="D13">
-        <v>0.4519621337958818</v>
+        <v>0.1990910114627568</v>
       </c>
       <c r="E13">
         <v>0.09767929089444222</v>
       </c>
       <c r="F13">
-        <v>0.1296414246903223</v>
+        <v>-0.1232296976428027</v>
       </c>
       <c r="G13">
-        <v>-0.03196213379588009</v>
+        <v>0.2209089885372449</v>
       </c>
       <c r="H13">
-        <v>0.03196213379588009</v>
+        <v>0.02555040674836048</v>
       </c>
       <c r="I13">
-        <v>0.007265655126095449</v>
+        <v>0.005644314511495512</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -915,22 +915,22 @@
         <v>0.5</v>
       </c>
       <c r="D14">
-        <v>0.4767931333449341</v>
+        <v>0.295306589255621</v>
       </c>
       <c r="E14">
         <v>-0.3179231863442404</v>
       </c>
       <c r="F14">
-        <v>-0.3411300529993063</v>
+        <v>-0.5226165970886194</v>
       </c>
       <c r="G14">
-        <v>0.02320686665506588</v>
+        <v>0.204693410744379</v>
       </c>
       <c r="H14">
-        <v>0.02320686665506588</v>
+        <v>0.204693410744379</v>
       </c>
       <c r="I14">
-        <v>0.01529456064403491</v>
+        <v>0.1720529551372137</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -953,22 +953,22 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D15">
-        <v>0.510024272622684</v>
+        <v>0.42801824344899</v>
       </c>
       <c r="E15">
         <v>0.333762301286916</v>
       </c>
       <c r="F15">
-        <v>0.4437865739095943</v>
+        <v>0.3617805447359003</v>
       </c>
       <c r="G15">
-        <v>-0.1100242726226783</v>
+        <v>-0.02801824344898429</v>
       </c>
       <c r="H15">
-        <v>0.1100242726226783</v>
+        <v>0.02801824344898429</v>
       </c>
       <c r="I15">
-        <v>0.08554924942207774</v>
+        <v>0.01948788878906667</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
@@ -991,31 +991,31 @@
         <v>0.4200000000000017</v>
       </c>
       <c r="D16">
-        <v>0.4432850384870622</v>
+        <v>0.2209297857152165</v>
       </c>
       <c r="E16">
         <v>0.1476995305164278</v>
       </c>
       <c r="F16">
-        <v>0.1709845690034883</v>
+        <v>-0.05137068376835741</v>
       </c>
       <c r="G16">
-        <v>-0.02328503848706048</v>
+        <v>0.1990702142847852</v>
       </c>
       <c r="H16">
-        <v>0.02328503848706048</v>
+        <v>-0.09632884674807041</v>
       </c>
       <c r="I16">
-        <v>0.00742057152253546</v>
+        <v>-0.01917620416394461</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1029,31 +1029,31 @@
         <v>0.4200000000000017</v>
       </c>
       <c r="D17">
-        <v>0.4644851198714784</v>
+        <v>0.3248074065376587</v>
       </c>
       <c r="E17">
         <v>0.1040735922691067</v>
       </c>
       <c r="F17">
-        <v>0.1485587121405834</v>
+        <v>0.00888099880676374</v>
       </c>
       <c r="G17">
-        <v>-0.04448511987147669</v>
+        <v>0.09519259346234299</v>
       </c>
       <c r="H17">
-        <v>0.04448511987147669</v>
+        <v>-0.09519259346234299</v>
       </c>
       <c r="I17">
-        <v>0.01123837834507246</v>
+        <v>-0.01075244046799053</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1067,31 +1067,31 @@
         <v>0.4490000000000123</v>
       </c>
       <c r="D18">
-        <v>0.4674964599682822</v>
+        <v>0.3206844565877573</v>
       </c>
       <c r="E18">
         <v>-0.216311402698194</v>
       </c>
       <c r="F18">
-        <v>-0.1978149427299241</v>
+        <v>-0.344626946110449</v>
       </c>
       <c r="G18">
-        <v>-0.01849645996826993</v>
+        <v>0.128315543412255</v>
       </c>
       <c r="H18">
-        <v>-0.01849645996826993</v>
+        <v>0.128315543412255</v>
       </c>
       <c r="I18">
-        <v>-0.007659871370017106</v>
+        <v>0.07197710904815408</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1105,31 +1105,31 @@
         <v>0.4399999999999977</v>
       </c>
       <c r="D19">
-        <v>0.491323943849979</v>
+        <v>0.4160066403303275</v>
       </c>
       <c r="E19">
         <v>0.2488650222990841</v>
       </c>
       <c r="F19">
-        <v>0.3001889661490654</v>
+        <v>0.2248716626294139</v>
       </c>
       <c r="G19">
-        <v>-0.05132394384998129</v>
+        <v>0.0239933596696702</v>
       </c>
       <c r="H19">
-        <v>0.05132394384998129</v>
+        <v>-0.0239933596696702</v>
       </c>
       <c r="I19">
-        <v>0.02817961607372111</v>
+        <v>-0.01136653467020668</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1143,31 +1143,31 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D20">
-        <v>0.4590295182052229</v>
+        <v>0.3267011784016723</v>
       </c>
       <c r="E20">
         <v>-0.2058961837583608</v>
       </c>
       <c r="F20">
-        <v>-0.1468666655531436</v>
+        <v>-0.2791950053566942</v>
       </c>
       <c r="G20">
-        <v>-0.05902951820521724</v>
+        <v>0.0732988215983334</v>
       </c>
       <c r="H20">
-        <v>-0.05902951820521724</v>
+        <v>0.0732988215983334</v>
       </c>
       <c r="I20">
-        <v>-0.02082342103555775</v>
+        <v>0.03555661252986783</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1181,22 +1181,22 @@
         <v>0.5999999999999943</v>
       </c>
       <c r="D21">
-        <v>0.4890110279974841</v>
+        <v>0.4348877705518358</v>
       </c>
       <c r="E21">
         <v>-0.2241758241758233</v>
       </c>
       <c r="F21">
-        <v>-0.3351647961783335</v>
+        <v>-0.3892880536239818</v>
       </c>
       <c r="G21">
-        <v>0.1109889720025102</v>
+        <v>0.1651122294481585</v>
       </c>
       <c r="H21">
-        <v>0.1109889720025102</v>
+        <v>0.1651122294481585</v>
       </c>
       <c r="I21">
-        <v>0.06208064045235422</v>
+        <v>0.1012903885494385</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -1219,31 +1219,31 @@
         <v>0.4999999999999858</v>
       </c>
       <c r="D22">
-        <v>0.512109277166932</v>
+        <v>0.487700655685696</v>
       </c>
       <c r="E22">
         <v>0.2027192445571344</v>
       </c>
       <c r="F22">
-        <v>0.2148285217240806</v>
+        <v>0.1904199002428446</v>
       </c>
       <c r="G22">
-        <v>-0.01210927716694621</v>
+        <v>0.01229934431428981</v>
       </c>
       <c r="H22">
-        <v>0.01210927716694621</v>
+        <v>-0.01229934431428981</v>
       </c>
       <c r="I22">
-        <v>0.005056201632338511</v>
+        <v>-0.004835353705320379</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1257,25 +1257,25 @@
         <v>0.6150000000000091</v>
       </c>
       <c r="D23">
-        <v>0.4975826625273121</v>
+        <v>0.4479022197997632</v>
       </c>
       <c r="E23">
         <v>0.1634151107251537</v>
       </c>
       <c r="F23">
-        <v>0.04599777325245669</v>
+        <v>-0.003682669475092215</v>
       </c>
       <c r="G23">
-        <v>0.117417337472697</v>
+        <v>0.1670977802002459</v>
       </c>
       <c r="H23">
-        <v>-0.117417337472697</v>
+        <v>-0.1597324412500615</v>
       </c>
       <c r="I23">
-        <v>-0.02458870326912982</v>
+        <v>-0.02669093635885146</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -1295,31 +1295,31 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D24">
-        <v>0.4740277436429943</v>
+        <v>0.3585940925853104</v>
       </c>
       <c r="E24">
         <v>0.5988415319443334</v>
       </c>
       <c r="F24">
-        <v>0.6728692755873221</v>
+        <v>0.5574356245296381</v>
       </c>
       <c r="G24">
-        <v>-0.07402774364298864</v>
+        <v>0.0414059074146953</v>
       </c>
       <c r="H24">
-        <v>0.0740277436429887</v>
+        <v>-0.0414059074146953</v>
       </c>
       <c r="I24">
-        <v>0.09414188164797149</v>
+        <v>-0.04787670488668844</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1333,22 +1333,22 @@
         <v>0.4999999999999858</v>
       </c>
       <c r="D25">
-        <v>0.4852764170883958</v>
+        <v>0.3695560017914198</v>
       </c>
       <c r="E25">
         <v>0.4826764833261045</v>
       </c>
       <c r="F25">
-        <v>0.4679529004145144</v>
+        <v>0.3522324851175385</v>
       </c>
       <c r="G25">
-        <v>0.01472358291158998</v>
+        <v>0.130443998208566</v>
       </c>
       <c r="H25">
-        <v>-0.01472358291159004</v>
+        <v>-0.130443998208566</v>
       </c>
       <c r="I25">
-        <v>-0.01399667054969875</v>
+        <v>-0.1089088639839783</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
@@ -1371,31 +1371,31 @@
         <v>0.4</v>
       </c>
       <c r="D26">
-        <v>0.4378187151066742</v>
+        <v>0.2277325139290328</v>
       </c>
       <c r="E26">
         <v>-0.02435264570883766</v>
       </c>
       <c r="F26">
-        <v>0.01346606939783651</v>
+        <v>-0.1966201317798049</v>
       </c>
       <c r="G26">
-        <v>-0.03781871510667417</v>
+        <v>0.1722674860709672</v>
       </c>
       <c r="H26">
-        <v>-0.01088657631100115</v>
+        <v>0.1722674860709672</v>
       </c>
       <c r="I26">
-        <v>-0.0004117163279928204</v>
+        <v>0.03806642486808767</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1409,31 +1409,31 @@
         <v>0.2999999999999829</v>
       </c>
       <c r="D27">
-        <v>0.4462795520620876</v>
+        <v>0.2525395772002005</v>
       </c>
       <c r="E27">
         <v>0.374689571468565</v>
       </c>
       <c r="F27">
-        <v>0.5209691235306697</v>
+        <v>0.3272291486687826</v>
       </c>
       <c r="G27">
-        <v>-0.1462795520621047</v>
+        <v>0.04746042279978241</v>
       </c>
       <c r="H27">
-        <v>0.1462795520621047</v>
+        <v>-0.04746042279978241</v>
       </c>
       <c r="I27">
-        <v>0.1310165527050173</v>
+        <v>-0.03331335922880066</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1447,22 +1447,22 @@
         <v>0.3</v>
       </c>
       <c r="D28">
-        <v>0.4753692858281875</v>
+        <v>0.3362764478896823</v>
       </c>
       <c r="E28">
         <v>0.2158406583130695</v>
       </c>
       <c r="F28">
-        <v>0.391209944141257</v>
+        <v>0.2521171062027519</v>
       </c>
       <c r="G28">
-        <v>-0.1753692858281875</v>
+        <v>-0.03627644788968232</v>
       </c>
       <c r="H28">
-        <v>0.1753692858281875</v>
+        <v>0.03627644788968232</v>
       </c>
       <c r="I28">
-        <v>0.1064580306139862</v>
+        <v>0.01697584545903042</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
@@ -1485,22 +1485,22 @@
         <v>0.09999999999999432</v>
       </c>
       <c r="D29">
-        <v>0.4250170430515021</v>
+        <v>0.2302697221081335</v>
       </c>
       <c r="E29">
         <v>0.07200447928330793</v>
       </c>
       <c r="F29">
-        <v>0.3970215223348157</v>
+        <v>0.2022742013914471</v>
       </c>
       <c r="G29">
-        <v>-0.3250170430515078</v>
+        <v>-0.1302697221081392</v>
       </c>
       <c r="H29">
-        <v>0.3250170430515078</v>
+        <v>0.1302697221081392</v>
       </c>
       <c r="I29">
-        <v>0.1524414441601943</v>
+        <v>0.03573020751168738</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
@@ -1523,31 +1523,31 @@
         <v>0.2399999999999949</v>
       </c>
       <c r="D30">
-        <v>0.4334571718570454</v>
+        <v>0.2388031018914837</v>
       </c>
       <c r="E30">
         <v>2.461807318894701</v>
       </c>
       <c r="F30">
-        <v>2.655264490751751</v>
+        <v>2.460610420786189</v>
       </c>
       <c r="G30">
-        <v>-0.1934571718570505</v>
+        <v>0.001196898108511202</v>
       </c>
       <c r="H30">
-        <v>0.1934571718570504</v>
+        <v>-0.001196898108511313</v>
       </c>
       <c r="I30">
-        <v>0.9899342404836418</v>
+        <v>-0.005891632481926479</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1561,22 +1561,22 @@
         <v>-4.500000000000028</v>
       </c>
       <c r="D31">
-        <v>0.429003595455585</v>
+        <v>0.2309795650301406</v>
       </c>
       <c r="E31">
         <v>5.19095764975197</v>
       </c>
       <c r="F31">
-        <v>10.11996124520758</v>
+        <v>9.92193721478214</v>
       </c>
       <c r="G31">
-        <v>-4.929003595455614</v>
+        <v>-4.730979565030169</v>
       </c>
       <c r="H31">
-        <v>4.929003595455614</v>
+        <v>4.73097956503017</v>
       </c>
       <c r="I31">
-        <v>75.46757428298494</v>
+        <v>71.49879677256027</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
@@ -1599,22 +1599,22 @@
         <v>6.9</v>
       </c>
       <c r="D32">
-        <v>0.1845625379573629</v>
+        <v>-0.2984254746956241</v>
       </c>
       <c r="E32">
         <v>-1.580304150385469</v>
       </c>
       <c r="F32">
-        <v>-8.295741612428106</v>
+        <v>-8.778729625081095</v>
       </c>
       <c r="G32">
-        <v>6.715437462042638</v>
+        <v>7.198425474695624</v>
       </c>
       <c r="H32">
-        <v>6.715437462042637</v>
+        <v>7.198425474695625</v>
       </c>
       <c r="I32">
-        <v>66.32196769244572</v>
+        <v>74.56873262255091</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
@@ -1637,22 +1637,22 @@
         <v>2.752121286959607</v>
       </c>
       <c r="D33">
-        <v>-1.193206222023147</v>
+        <v>-5.824773328900056</v>
       </c>
       <c r="E33">
         <v>2.411488683553286</v>
       </c>
       <c r="F33">
-        <v>-1.533838825429467</v>
+        <v>-6.165405932306377</v>
       </c>
       <c r="G33">
-        <v>3.945327508982754</v>
+        <v>8.576894615859663</v>
       </c>
       <c r="H33">
-        <v>-0.8776498581238188</v>
+        <v>3.753917248753091</v>
       </c>
       <c r="I33">
-        <v>-3.462616128510713</v>
+        <v>32.1969526392131</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -1675,22 +1675,22 @@
         <v>0.5884439773270884</v>
       </c>
       <c r="D34">
-        <v>1.261165603092325</v>
+        <v>2.839500349044278</v>
       </c>
       <c r="E34">
         <v>2.39538184572016</v>
       </c>
       <c r="F34">
-        <v>3.068103471485397</v>
+        <v>4.64643821743735</v>
       </c>
       <c r="G34">
-        <v>-0.6727216257652366</v>
+        <v>-2.25105637171719</v>
       </c>
       <c r="H34">
-        <v>0.6727216257652371</v>
+        <v>2.25105637171719</v>
       </c>
       <c r="I34">
-        <v>3.675404724935025</v>
+        <v>15.85153392165666</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
@@ -1713,22 +1713,22 @@
         <v>2.056410000000014</v>
       </c>
       <c r="D35">
-        <v>0.4476168619322896</v>
+        <v>0.484767524391212</v>
       </c>
       <c r="E35">
         <v>0.4233178818697558</v>
       </c>
       <c r="F35">
-        <v>-1.185475256197968</v>
+        <v>-1.148324593739046</v>
       </c>
       <c r="G35">
-        <v>1.608793138067724</v>
+        <v>1.571642475608802</v>
       </c>
       <c r="H35">
-        <v>0.7621573743282126</v>
+        <v>0.7250067118692902</v>
       </c>
       <c r="I35">
-        <v>1.226153553946942</v>
+        <v>1.139451343475249</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
@@ -1751,22 +1751,22 @@
         <v>3.560000000000002</v>
       </c>
       <c r="D36">
-        <v>0.5360215555148026</v>
+        <v>0.5695283982339502</v>
       </c>
       <c r="E36">
         <v>1.865733703455543</v>
       </c>
       <c r="F36">
-        <v>-1.158244741029657</v>
+        <v>-1.124737898310509</v>
       </c>
       <c r="G36">
-        <v>3.023978444485199</v>
+        <v>2.990471601766052</v>
       </c>
       <c r="H36">
-        <v>-0.7074889624258862</v>
+        <v>-0.740995805145034</v>
       </c>
       <c r="I36">
-        <v>-2.139431372087079</v>
+        <v>-2.215926912313995</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
@@ -1789,22 +1789,22 @@
         <v>1.299999999999983</v>
       </c>
       <c r="D37">
-        <v>0.3757945368741529</v>
+        <v>-0.03119439636203225</v>
       </c>
       <c r="E37">
         <v>1.647189640611778</v>
       </c>
       <c r="F37">
-        <v>0.7229841774859482</v>
+        <v>0.3159952442497632</v>
       </c>
       <c r="G37">
-        <v>0.9242054631258301</v>
+        <v>1.331194396362015</v>
       </c>
       <c r="H37">
-        <v>-0.9242054631258301</v>
+        <v>-1.331194396362015</v>
       </c>
       <c r="I37">
-        <v>-2.190527591243726</v>
+        <v>-2.613380717750292</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
@@ -1827,22 +1827,22 @@
         <v>-0.01</v>
       </c>
       <c r="D38">
-        <v>0.4165402662730592</v>
+        <v>0.411781671159695</v>
       </c>
       <c r="E38">
         <v>-0.2454048964218456</v>
       </c>
       <c r="F38">
-        <v>0.1811353698512136</v>
+        <v>0.1763767747378494</v>
       </c>
       <c r="G38">
-        <v>-0.4265402662730592</v>
+        <v>-0.421781671159695</v>
       </c>
       <c r="H38">
-        <v>-0.06426952657063201</v>
+        <v>-0.06902812168399619</v>
       </c>
       <c r="I38">
-        <v>-0.02741354097668083</v>
+        <v>-0.02911479652089069</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
@@ -1865,22 +1865,22 @@
         <v>0.9923981685675987</v>
       </c>
       <c r="D39">
-        <v>0.5108515486168752</v>
+        <v>0.6435792755916881</v>
       </c>
       <c r="E39">
         <v>0.8526683129551109</v>
       </c>
       <c r="F39">
-        <v>0.3711216930043874</v>
+        <v>0.5038494199792003</v>
       </c>
       <c r="G39">
-        <v>0.4815466199507235</v>
+        <v>0.3488188929759105</v>
       </c>
       <c r="H39">
-        <v>-0.4815466199507235</v>
+        <v>-0.3488188929759106</v>
       </c>
       <c r="I39">
-        <v>-0.5893119408992722</v>
+        <v>-0.4731790139043385</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
@@ -1903,25 +1903,25 @@
         <v>1.170483608733242</v>
       </c>
       <c r="D40">
-        <v>0.4614622132961212</v>
+        <v>0.3223521558300787</v>
       </c>
       <c r="E40">
         <v>0.7703347161220313</v>
       </c>
       <c r="F40">
-        <v>0.06131332068491058</v>
+        <v>-0.07779673678113191</v>
       </c>
       <c r="G40">
-        <v>0.7090213954371207</v>
+        <v>0.8481314529031633</v>
       </c>
       <c r="H40">
-        <v>-0.7090213954371207</v>
+        <v>-0.6925379793408994</v>
       </c>
       <c r="I40">
-        <v>-0.5896562515693999</v>
+        <v>-0.5873632426090178</v>
       </c>
       <c r="J40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -1941,22 +1941,22 @@
         <v>-0.18</v>
       </c>
       <c r="D41">
-        <v>0.4745792891431377</v>
+        <v>0.4543915747020479</v>
       </c>
       <c r="E41">
         <v>0.2553061035472806</v>
       </c>
       <c r="F41">
-        <v>0.9098853926904182</v>
+        <v>0.8896976782493284</v>
       </c>
       <c r="G41">
-        <v>-0.6545792891431377</v>
+        <v>-0.6343915747020479</v>
       </c>
       <c r="H41">
-        <v>0.6545792891431377</v>
+        <v>0.6343915747020479</v>
       </c>
       <c r="I41">
-        <v>0.7627102213229018</v>
+        <v>0.7263807521737508</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
@@ -1979,22 +1979,22 @@
         <v>-0.39</v>
       </c>
       <c r="D42">
-        <v>0.4590343884134018</v>
+        <v>0.3117430721575033</v>
       </c>
       <c r="E42">
         <v>-0.05477325635534092</v>
       </c>
       <c r="F42">
-        <v>0.7942611320580608</v>
+        <v>0.6469698158021624</v>
       </c>
       <c r="G42">
-        <v>-0.8490343884134017</v>
+        <v>-0.7017430721575033</v>
       </c>
       <c r="H42">
-        <v>0.7394878757027199</v>
+        <v>0.5921965594468215</v>
       </c>
       <c r="I42">
-        <v>0.6278506362863845</v>
+        <v>0.415569832947316</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
@@ -2017,22 +2017,22 @@
         <v>0.06486426577477289</v>
       </c>
       <c r="D43">
-        <v>0.485462993517302</v>
+        <v>0.4307600866690486</v>
       </c>
       <c r="E43">
         <v>0.04630450333973575</v>
       </c>
       <c r="F43">
-        <v>0.4669032310822648</v>
+        <v>0.4122003242340114</v>
       </c>
       <c r="G43">
-        <v>-0.4205987277425291</v>
+        <v>-0.3658958208942757</v>
       </c>
       <c r="H43">
-        <v>0.4205987277425291</v>
+        <v>0.3658958208942757</v>
       </c>
       <c r="I43">
-        <v>0.2158545201655192</v>
+        <v>0.1677650002690846</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
@@ -2055,22 +2055,22 @@
         <v>0.18</v>
       </c>
       <c r="D44">
-        <v>0.4684671993835729</v>
+        <v>0.2226830363001488</v>
       </c>
       <c r="E44">
         <v>0.3096176279974082</v>
       </c>
       <c r="F44">
-        <v>0.5980848273809811</v>
+        <v>0.352300664297557</v>
       </c>
       <c r="G44">
-        <v>-0.2884671993835729</v>
+        <v>-0.0426830363001488</v>
       </c>
       <c r="H44">
-        <v>0.2884671993835729</v>
+        <v>0.0426830363001488</v>
       </c>
       <c r="I44">
-        <v>0.2618423851765965</v>
+        <v>0.0282526824977585</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
@@ -2093,31 +2093,31 @@
         <v>0.32</v>
       </c>
       <c r="D45">
-        <v>0.4647694966202552</v>
+        <v>0.2651495229949266</v>
       </c>
       <c r="E45">
         <v>0.6070636170015632</v>
       </c>
       <c r="F45">
-        <v>0.7518331136218184</v>
+        <v>0.5522131399964898</v>
       </c>
       <c r="G45">
-        <v>-0.1447694966202552</v>
+        <v>0.05485047700507339</v>
       </c>
       <c r="H45">
-        <v>0.1447694966202552</v>
+        <v>-0.05485047700507339</v>
       </c>
       <c r="I45">
-        <v>0.1967267956512574</v>
+        <v>-0.06358688310223776</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2131,22 +2131,22 @@
         <v>0.2939713448086394</v>
       </c>
       <c r="D46">
-        <v>0.4698881152139972</v>
+        <v>0.3038735987643086</v>
       </c>
       <c r="E46">
         <v>0.08037550528413179</v>
       </c>
       <c r="F46">
-        <v>0.2562922756894896</v>
+        <v>0.09027775923980097</v>
       </c>
       <c r="G46">
-        <v>-0.1759167704053578</v>
+        <v>-0.009902253955669182</v>
       </c>
       <c r="H46">
-        <v>0.1759167704053578</v>
+        <v>0.009902253955669182</v>
       </c>
       <c r="I46">
-        <v>0.05922550872841784</v>
+        <v>0.001689851963679972</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
@@ -2169,22 +2169,22 @@
         <v>0.2143578612482884</v>
       </c>
       <c r="D47">
-        <v>0.4709254730754072</v>
+        <v>0.2992822907967085</v>
       </c>
       <c r="E47">
         <v>0.2811199022592499</v>
       </c>
       <c r="F47">
-        <v>0.5376875140863687</v>
+        <v>0.36604433180767</v>
       </c>
       <c r="G47">
-        <v>-0.2565676118271188</v>
+        <v>-0.08492442954842008</v>
       </c>
       <c r="H47">
-        <v>0.2565676118271188</v>
+        <v>0.08492442954842011</v>
       </c>
       <c r="I47">
-        <v>0.2100794633581287</v>
+        <v>0.05496005340227342</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
@@ -2207,31 +2207,31 @@
         <v>0.43</v>
       </c>
       <c r="D48">
-        <v>0.4484823066309763</v>
+        <v>0.1587597609686054</v>
       </c>
       <c r="E48">
         <v>0.3247871831659499</v>
       </c>
       <c r="F48">
-        <v>0.3432694897969262</v>
+        <v>0.0535469441345553</v>
       </c>
       <c r="G48">
-        <v>-0.01848230663097633</v>
+        <v>0.2712402390313946</v>
       </c>
       <c r="H48">
-        <v>0.01848230663097633</v>
+        <v>-0.2712402390313946</v>
       </c>
       <c r="I48">
-        <v>0.01234722827656975</v>
+        <v>-0.1026194391227231</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2245,22 +2245,22 @@
         <v>0.21</v>
       </c>
       <c r="D49">
-        <v>0.4673793252075983</v>
+        <v>0.3084674976711596</v>
       </c>
       <c r="E49">
         <v>0.4106497229122814</v>
       </c>
       <c r="F49">
-        <v>0.6680290481198796</v>
+        <v>0.509117220583441</v>
       </c>
       <c r="G49">
-        <v>-0.2573793252075983</v>
+        <v>-0.09846749767115962</v>
       </c>
       <c r="H49">
-        <v>0.2573793252075982</v>
+        <v>0.09846749767115959</v>
       </c>
       <c r="I49">
-        <v>0.2776296142040189</v>
+        <v>0.09056714936667465</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
@@ -2283,25 +2283,25 @@
         <v>0.1997641087852884</v>
       </c>
       <c r="D50">
-        <v>0.45559737055997</v>
+        <v>0.2200184630523081</v>
       </c>
       <c r="E50">
         <v>-0.2119161209897164</v>
       </c>
       <c r="F50">
-        <v>0.04391714078496523</v>
+        <v>-0.1916617667226967</v>
       </c>
       <c r="G50">
-        <v>-0.2558332617746816</v>
+        <v>-0.02025435426701969</v>
       </c>
       <c r="H50">
-        <v>-0.1679989802047512</v>
+        <v>-0.02025435426701969</v>
       </c>
       <c r="I50">
-        <v>-0.04297972708060166</v>
+        <v>-0.008174209512062706</v>
       </c>
       <c r="J50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="b">
         <v>1</v>
@@ -2321,22 +2321,22 @@
         <v>0.2008403794809794</v>
       </c>
       <c r="D51">
-        <v>0.4645309466893844</v>
+        <v>0.3078859509171186</v>
       </c>
       <c r="E51">
         <v>0.4775315349050862</v>
       </c>
       <c r="F51">
-        <v>0.741222102113491</v>
+        <v>0.5845771063412253</v>
       </c>
       <c r="G51">
-        <v>-0.263690567208405</v>
+        <v>-0.1070455714361392</v>
       </c>
       <c r="H51">
-        <v>0.2636905672084049</v>
+        <v>0.1070455714361391</v>
       </c>
       <c r="I51">
-        <v>0.321373837832735</v>
+        <v>0.1136940264294727</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
@@ -2359,22 +2359,22 @@
         <v>0.09547648014918764</v>
       </c>
       <c r="D52">
-        <v>0.4419561689885529</v>
+        <v>0.1965658720679752</v>
       </c>
       <c r="E52">
         <v>0.09547648014918764</v>
       </c>
       <c r="F52">
-        <v>0.4419561689885529</v>
+        <v>0.1965658720679752</v>
       </c>
       <c r="G52">
-        <v>-0.3464796888393653</v>
+        <v>-0.1010893919187876</v>
       </c>
       <c r="H52">
-        <v>0.3464796888393653</v>
+        <v>0.1010893919187876</v>
       </c>
       <c r="I52">
-        <v>0.1862094970453601</v>
+        <v>0.02952238380016538</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
